--- a/1-100.xlsx
+++ b/1-100.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cord\personal\quiz_sakumon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1D9879-9A14-4226-BE46-32C47D7B7B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA2B7CB-6BE5-4BBF-A8D0-3D0CE5DB6132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -119,9 +119,6 @@
   </si>
   <si>
     <t>サブウェイ(SUBWAY)</t>
-  </si>
-  <si>
-    <t>今年5月には書籍の表紙デザインをモチーフにしたTシャツの販売を始めた、「広辞苑」の出版社はどこでしょう？</t>
   </si>
   <si>
     <t>岩波書店</t>
@@ -220,6 +217,125 @@
     <t>肺</t>
     <rPh sb="0" eb="1">
       <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今年(2026年)5月には書籍の表紙デザインをモチーフにしたTシャツの販売を始めた、「広辞苑」の出版社はどこでしょう？</t>
+    <rPh sb="7" eb="8">
+      <t>ネン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TOP CONNECT株式会社が手がけ、現役大学生が企画、取材打診、執筆までを行う、毎年4月と10月の年2回発行され、大学や専門学校に配布されているフリーペーパーは何でしょう？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>学生新聞</t>
+    <rPh sb="0" eb="4">
+      <t>ガクセイシンブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>長時間かかるタスクの進捗状況がどの程度完了したのかを表示する、横長四角のGUIは何でしょう？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プログレスバー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今年4月に気象庁が新たに追加した予報用語である、最高気温が40℃以上の日の名称を何というでしょう？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>酷暑日</t>
+    <rPh sb="0" eb="3">
+      <t>コクショビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「龍と苺」「ハチワンダイバー」「3月のライオン」などの漫画の主人公がプレイする遊戯は何でしょう？</t>
+  </si>
+  <si>
+    <t>将棋</t>
+    <rPh sb="0" eb="2">
+      <t>ショウギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今年(2026年)は7月18日に放送された、『音楽のチカラで日本を元気に！』という願いを込めて2011年から始まった、TBS系列で毎年夏に生放送される長時間の音楽特番は何でしょう？</t>
+    <rPh sb="7" eb="8">
+      <t>ネン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音楽の日</t>
+    <rPh sb="0" eb="2">
+      <t>オンガク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今年(2026年)で発売から75年目を迎える、バレンシアオレンジ果汁を使用し、酸味と甘味のバランスがとれた味わいが特徴的なアサヒ飲料の果汁飲料は何でしょう？</t>
+    <rPh sb="7" eb="8">
+      <t>ネン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">バヤリースオレンジ </t>
+  </si>
+  <si>
+    <t>合言葉を『いつまでも色褪せない衝撃』とし、東京・下北沢を中心に店舗や公演を展開している、株式会社グリーンダイスが運営する謎解きレーベルは何でしょう？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タンブルウィード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「きなこ」や「みたらし」という味が発売され、食感からその名前がついた、ミスタードーナツの話題となった商品を何と言うでしょう？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>もっちゅりん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>匿名ラジオ</t>
+    <rPh sb="0" eb="2">
+      <t>トクメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1998年のFIFAワールドカップ本大会で日本代表のW杯初ゴールを決めたサッカー選手は誰でしょう？</t>
+  </si>
+  <si>
+    <t>今年(2026年)で10周年を迎える、ダ・ヴィンチ・恐山とARuFaがパーソナリティを務めるwebラジオは何でしょう？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中山 雅史(なかやままさし)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大分県では大分市についで2番目に人口が多い、濁音と半濁音が両方含まれる都市はどこでしょう？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>別府市</t>
+    <rPh sb="0" eb="3">
+      <t>ベップシ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -264,8 +380,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -550,7 +672,7 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="88.9140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="88.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -723,10 +845,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" t="s">
         <v>31</v>
-      </c>
-      <c r="C16" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -734,10 +856,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
         <v>33</v>
-      </c>
-      <c r="C17" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -745,10 +867,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
         <v>35</v>
-      </c>
-      <c r="C18" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -756,10 +878,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
         <v>37</v>
-      </c>
-      <c r="C19" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -767,10 +889,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
         <v>39</v>
-      </c>
-      <c r="C20" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -778,10 +900,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
         <v>41</v>
-      </c>
-      <c r="C21" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -789,10 +911,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -800,10 +922,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s">
         <v>45</v>
-      </c>
-      <c r="C23" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -811,10 +933,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" t="s">
         <v>47</v>
-      </c>
-      <c r="C24" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -822,10 +944,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" t="s">
         <v>49</v>
-      </c>
-      <c r="C25" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -833,10 +955,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" t="s">
         <v>51</v>
-      </c>
-      <c r="C26" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -844,10 +966,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" t="s">
         <v>53</v>
-      </c>
-      <c r="C27" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -855,10 +977,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" t="s">
         <v>55</v>
-      </c>
-      <c r="C28" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -866,10 +988,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" t="s">
         <v>57</v>
-      </c>
-      <c r="C29" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -877,98 +999,164 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" t="s">
         <v>59</v>
-      </c>
-      <c r="C30" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
         <v>30</v>
       </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:1">
+      <c r="B32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="B34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="B35" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="B36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="B38" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="B39" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="B40" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:1">
+      <c r="B41" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:3">
       <c r="A43">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:3">
       <c r="A44">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:3">
       <c r="A45">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:3">
       <c r="A46">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:3">
       <c r="A47">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:3">
       <c r="A48">
         <v>47</v>
       </c>
